--- a/artfynd/A 12715-2026 artfynd.xlsx
+++ b/artfynd/A 12715-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68151244</v>
+        <v>128989385</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedere Högbergsåravinen, Dlr</t>
+          <t>Högbergsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512678.0576877886</v>
+        <v>512772</v>
       </c>
       <c r="R2" t="n">
-        <v>6695029.82359631</v>
+        <v>6695045</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,28 +757,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Hedblandskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog i erosionsraviner</t>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,7 +804,7 @@
         <v>128989360</v>
       </c>
       <c r="B3" t="n">
-        <v>86897</v>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,10 +920,745 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Anders Janols, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128989743</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högbergsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>512651</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6695149</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128989748</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högbergsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512668</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6695135</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68151185</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nedere Högbergsåravinen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512678</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6695030</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Hedblandskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog i erosionsraviner</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Janols</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Janols, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103780153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högbergsåravinen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512749</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6695016</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera hundra bladrosetter inom ett större område. På åsen söder om ravinen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Uno Skog, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132255101</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98054</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högbergsåravinen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512607</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6695049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>ravinsystem</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128989756</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högbergsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512668</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6695135</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
